--- a/Outbound Dataset.xlsx
+++ b/Outbound Dataset.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -47,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1232,6 +1234,9 @@
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
@@ -1282,6 +1287,21 @@
       <c r="CN2" t="inlineStr">
         <is>
           <t>&lt;div style="text-align:center"&gt;&lt;img height="80px" src="https://KB-prod-images-1.s3.ap-south-1.amazonaws.com/LSEB00021BLACK.PNG"&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Not Invoiced</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Yet to ship</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Short Received</t>
         </is>
       </c>
       <c r="DB2" t="n">
@@ -1470,6 +1490,9 @@
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
@@ -1520,6 +1543,21 @@
       <c r="CN3" t="inlineStr">
         <is>
           <t>&lt;div style="text-align:center"&gt;&lt;img height="80px" src="https://KB-prod-images-1.s3.ap-south-1.amazonaws.com/YWJ00014OLIVE.PNG"&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>Not Invoiced</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>Yet to ship</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>Short Received</t>
         </is>
       </c>
       <c r="DB3" t="n">
@@ -1703,6 +1741,9 @@
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
@@ -1753,6 +1794,21 @@
       <c r="CN4" t="inlineStr">
         <is>
           <t>&lt;div style="text-align:center"&gt;&lt;img height="80px" src="https://KB-prod-images-1.s3.ap-south-1.amazonaws.com/NEFK00017CLOUD_DANCER.PNG"&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>Not Invoiced</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>Yet to ship</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>Short Received</t>
         </is>
       </c>
       <c r="DB4" t="n">
@@ -1941,6 +1997,9 @@
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
@@ -1991,6 +2050,21 @@
       <c r="CN5" t="inlineStr">
         <is>
           <t>&lt;div style="text-align:center"&gt;&lt;img height="80px" src="https://KB-prod-images-1.s3.ap-south-1.amazonaws.com/YWJ00013OCEAN_BLUE.PNG"&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>Not Invoiced</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>Yet to ship</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>Short Received</t>
         </is>
       </c>
       <c r="DB5" t="n">
@@ -2143,6 +2217,9 @@
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
@@ -2188,6 +2265,11 @@
       <c r="CN6" t="inlineStr">
         <is>
           <t>&lt;div style="text-align:center"&gt;&lt;img height="80px" src="https://i.imgur.com/e9zmAss.png"&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>Not Invoiced</t>
         </is>
       </c>
       <c r="CQ6" s="1" t="n">
@@ -2817,6 +2899,25 @@
       <c r="BR8" t="n">
         <v>1</v>
       </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>8909001188644</t>
+        </is>
+      </c>
+      <c r="BU8" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1</v>
+      </c>
       <c r="BX8" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909001188644</t>
@@ -3190,6 +3291,25 @@
       <c r="BR9" t="n">
         <v>1</v>
       </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>8909404139441</t>
+        </is>
+      </c>
+      <c r="BU9" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1</v>
+      </c>
       <c r="BX9" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909404139441</t>
@@ -3563,6 +3683,25 @@
       <c r="BR10" t="n">
         <v>1</v>
       </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>8909404231152</t>
+        </is>
+      </c>
+      <c r="BU10" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1</v>
+      </c>
       <c r="BX10" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909404231152</t>
@@ -3936,6 +4075,25 @@
       <c r="BR11" t="n">
         <v>1</v>
       </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>8909404231947</t>
+        </is>
+      </c>
+      <c r="BU11" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1</v>
+      </c>
       <c r="BX11" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909404231947</t>
@@ -4309,6 +4467,25 @@
       <c r="BR12" t="n">
         <v>1</v>
       </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>8909404231947</t>
+        </is>
+      </c>
+      <c r="BU12" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1</v>
+      </c>
       <c r="BX12" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909404231947</t>
@@ -4682,6 +4859,25 @@
       <c r="BR13" t="n">
         <v>1</v>
       </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>C260bJ4z02</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>8909404320306</t>
+        </is>
+      </c>
+      <c r="BU13" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1</v>
+      </c>
       <c r="BX13" t="inlineStr">
         <is>
           <t>C260bJ4z02-2026-08-05-8909404320306</t>
@@ -5055,6 +5251,25 @@
       <c r="BR14" t="n">
         <v>1</v>
       </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>C260xPYk02</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>8909001100417</t>
+        </is>
+      </c>
+      <c r="BU14" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1</v>
+      </c>
       <c r="BX14" t="inlineStr">
         <is>
           <t>C260xPYk02-2026-08-05-8909001100417</t>
@@ -5433,6 +5648,25 @@
       <c r="BR15" t="n">
         <v>1</v>
       </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>C264xahw01</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>8907546855991</t>
+        </is>
+      </c>
+      <c r="BU15" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1</v>
+      </c>
       <c r="BX15" t="inlineStr">
         <is>
           <t>C264xahw01-2026-08-05-8907546855991</t>
@@ -5806,6 +6040,25 @@
       <c r="BR16" t="n">
         <v>1</v>
       </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>C265dxvz01</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>8909404133432</t>
+        </is>
+      </c>
+      <c r="BU16" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1</v>
+      </c>
       <c r="BX16" t="inlineStr">
         <is>
           <t>C265dxvz01-2026-08-05-8909404133432</t>
@@ -6515,6 +6768,25 @@
       <c r="BR18" t="n">
         <v>1</v>
       </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>C268abdo01</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>8909404017794</t>
+        </is>
+      </c>
+      <c r="BU18" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1</v>
+      </c>
       <c r="BX18" t="inlineStr">
         <is>
           <t>C268abdo01-2026-08-05-8909404017794</t>
@@ -7881,6 +8153,25 @@
       <c r="BR22" t="n">
         <v>1</v>
       </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>C2696Guo01</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>8909404065481</t>
+        </is>
+      </c>
+      <c r="BU22" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1</v>
+      </c>
       <c r="BX22" t="inlineStr">
         <is>
           <t>C2696Guo01-2026-08-05-8909404065481</t>
@@ -8254,6 +8545,25 @@
       <c r="BR23" t="n">
         <v>1</v>
       </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>C2696Guo01</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>8909404065481</t>
+        </is>
+      </c>
+      <c r="BU23" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1</v>
+      </c>
       <c r="BX23" t="inlineStr">
         <is>
           <t>C2696Guo01-2026-08-05-8909404065481</t>
@@ -9289,6 +9599,25 @@
       <c r="BR26" t="n">
         <v>1</v>
       </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>C26cza2901</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>8909001907511</t>
+        </is>
+      </c>
+      <c r="BU26" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1</v>
+      </c>
       <c r="BX26" t="inlineStr">
         <is>
           <t>C26cza2901-2026-08-05-8909001907511</t>
@@ -9667,6 +9996,25 @@
       <c r="BR27" t="n">
         <v>1</v>
       </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>C26d9t2v01</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>8907546829138</t>
+        </is>
+      </c>
+      <c r="BU27" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1</v>
+      </c>
       <c r="BX27" t="inlineStr">
         <is>
           <t>C26d9t2v01-2026-08-05-8907546829138</t>
@@ -10376,6 +10724,25 @@
       <c r="BR29" t="n">
         <v>1</v>
       </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>C26e63wx01</t>
+        </is>
+      </c>
+      <c r="BT29" t="inlineStr">
+        <is>
+          <t>8909404151290</t>
+        </is>
+      </c>
+      <c r="BU29" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1</v>
+      </c>
       <c r="BX29" t="inlineStr">
         <is>
           <t>C26e63wx01-2026-08-05-8909404151290</t>
@@ -10749,6 +11116,25 @@
       <c r="BR30" t="n">
         <v>1</v>
       </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>C26eaJ8l01</t>
+        </is>
+      </c>
+      <c r="BT30" t="inlineStr">
+        <is>
+          <t>8909001929544</t>
+        </is>
+      </c>
+      <c r="BU30" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1</v>
+      </c>
       <c r="BX30" t="inlineStr">
         <is>
           <t>C26eaJ8l01-2026-08-05-8909001929544</t>
@@ -11122,6 +11508,25 @@
       <c r="BR31" t="n">
         <v>1</v>
       </c>
+      <c r="BS31" t="inlineStr">
+        <is>
+          <t>C26fc49u02</t>
+        </is>
+      </c>
+      <c r="BT31" t="inlineStr">
+        <is>
+          <t>8909001944400</t>
+        </is>
+      </c>
+      <c r="BU31" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1</v>
+      </c>
       <c r="BX31" t="inlineStr">
         <is>
           <t>C26fc49u02-2026-08-05-8909001944400</t>
@@ -11495,6 +11900,25 @@
       <c r="BR32" t="n">
         <v>1</v>
       </c>
+      <c r="BS32" t="inlineStr">
+        <is>
+          <t>C26hk87o01</t>
+        </is>
+      </c>
+      <c r="BT32" t="inlineStr">
+        <is>
+          <t>8909001723128</t>
+        </is>
+      </c>
+      <c r="BU32" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>1</v>
+      </c>
       <c r="BX32" t="inlineStr">
         <is>
           <t>C26hk87o01-2026-08-05-8909001723128</t>
@@ -12204,6 +12628,25 @@
       <c r="BR34" t="n">
         <v>1</v>
       </c>
+      <c r="BS34" t="inlineStr">
+        <is>
+          <t>C26iPl7J01</t>
+        </is>
+      </c>
+      <c r="BT34" t="inlineStr">
+        <is>
+          <t>8909001871485</t>
+        </is>
+      </c>
+      <c r="BU34" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>1</v>
+      </c>
       <c r="BX34" t="inlineStr">
         <is>
           <t>C26iPl7J01-2026-08-05-8909001871485</t>
@@ -12577,6 +13020,25 @@
       <c r="BR35" t="n">
         <v>1</v>
       </c>
+      <c r="BS35" t="inlineStr">
+        <is>
+          <t>C26iv97n01</t>
+        </is>
+      </c>
+      <c r="BT35" t="inlineStr">
+        <is>
+          <t>8909001321706</t>
+        </is>
+      </c>
+      <c r="BU35" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>1</v>
+      </c>
       <c r="BX35" t="inlineStr">
         <is>
           <t>C26iv97n01-2026-08-05-8909001321706</t>
@@ -12950,6 +13412,25 @@
       <c r="BR36" t="n">
         <v>1</v>
       </c>
+      <c r="BS36" t="inlineStr">
+        <is>
+          <t>C26iv97n01</t>
+        </is>
+      </c>
+      <c r="BT36" t="inlineStr">
+        <is>
+          <t>8909001330180</t>
+        </is>
+      </c>
+      <c r="BU36" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>1</v>
+      </c>
       <c r="BX36" t="inlineStr">
         <is>
           <t>C26iv97n01-2026-08-05-8909001330180</t>
@@ -13323,6 +13804,25 @@
       <c r="BR37" t="n">
         <v>1</v>
       </c>
+      <c r="BS37" t="inlineStr">
+        <is>
+          <t>C26izeQ501</t>
+        </is>
+      </c>
+      <c r="BT37" t="inlineStr">
+        <is>
+          <t>8909404144896</t>
+        </is>
+      </c>
+      <c r="BU37" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>1</v>
+      </c>
       <c r="BX37" t="inlineStr">
         <is>
           <t>C26izeQ501-2026-08-05-8909404144896</t>
@@ -14358,6 +14858,25 @@
       <c r="BR40" t="n">
         <v>1</v>
       </c>
+      <c r="BS40" t="inlineStr">
+        <is>
+          <t>C26Jnktk01</t>
+        </is>
+      </c>
+      <c r="BT40" t="inlineStr">
+        <is>
+          <t>8909404145695</t>
+        </is>
+      </c>
+      <c r="BU40" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>1</v>
+      </c>
       <c r="BX40" t="inlineStr">
         <is>
           <t>C26Jnktk01-2026-08-05-8909404145695</t>
@@ -14731,6 +15250,25 @@
       <c r="BR41" t="n">
         <v>1</v>
       </c>
+      <c r="BS41" t="inlineStr">
+        <is>
+          <t>C26Jnktk01</t>
+        </is>
+      </c>
+      <c r="BT41" t="inlineStr">
+        <is>
+          <t>8909404145695</t>
+        </is>
+      </c>
+      <c r="BU41" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>1</v>
+      </c>
       <c r="BX41" t="inlineStr">
         <is>
           <t>C26Jnktk01-2026-08-05-8909404145695</t>
@@ -16428,6 +16966,25 @@
       <c r="BR46" t="n">
         <v>1</v>
       </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>C26ko5r401</t>
+        </is>
+      </c>
+      <c r="BT46" t="inlineStr">
+        <is>
+          <t>8909001582077</t>
+        </is>
+      </c>
+      <c r="BU46" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>1</v>
+      </c>
       <c r="BX46" t="inlineStr">
         <is>
           <t>C26ko5r401-2026-08-05-8909001582077</t>
@@ -18792,6 +19349,25 @@
       <c r="BR53" t="n">
         <v>1</v>
       </c>
+      <c r="BS53" t="inlineStr">
+        <is>
+          <t>C26labPx01</t>
+        </is>
+      </c>
+      <c r="BT53" t="inlineStr">
+        <is>
+          <t>8907546896628</t>
+        </is>
+      </c>
+      <c r="BU53" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>1</v>
+      </c>
       <c r="BX53" t="inlineStr">
         <is>
           <t>C26labPx01-2026-08-05-8907546896628</t>
@@ -19170,6 +19746,25 @@
       <c r="BR54" t="n">
         <v>1</v>
       </c>
+      <c r="BS54" t="inlineStr">
+        <is>
+          <t>C26lGQvQ01</t>
+        </is>
+      </c>
+      <c r="BT54" t="inlineStr">
+        <is>
+          <t>8907546896772</t>
+        </is>
+      </c>
+      <c r="BU54" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1</v>
+      </c>
       <c r="BX54" t="inlineStr">
         <is>
           <t>C26lGQvQ01-2026-08-05-8907546896772</t>
@@ -20210,6 +20805,25 @@
       <c r="BR57" t="n">
         <v>1</v>
       </c>
+      <c r="BS57" t="inlineStr">
+        <is>
+          <t>C26n6ttv01</t>
+        </is>
+      </c>
+      <c r="BT57" t="inlineStr">
+        <is>
+          <t>8909001498736</t>
+        </is>
+      </c>
+      <c r="BU57" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1</v>
+      </c>
       <c r="BX57" t="inlineStr">
         <is>
           <t>C26n6ttv01-2026-08-05-8909001498736</t>
@@ -20588,6 +21202,25 @@
       <c r="BR58" t="n">
         <v>1</v>
       </c>
+      <c r="BS58" t="inlineStr">
+        <is>
+          <t>C26n6ttv01</t>
+        </is>
+      </c>
+      <c r="BT58" t="inlineStr">
+        <is>
+          <t>8909001498897</t>
+        </is>
+      </c>
+      <c r="BU58" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1</v>
+      </c>
       <c r="BX58" t="inlineStr">
         <is>
           <t>C26n6ttv01-2026-08-05-8909001498897</t>
@@ -20966,6 +21599,25 @@
       <c r="BR59" t="n">
         <v>1</v>
       </c>
+      <c r="BS59" t="inlineStr">
+        <is>
+          <t>C26n6ttv01</t>
+        </is>
+      </c>
+      <c r="BT59" t="inlineStr">
+        <is>
+          <t>8909001499832</t>
+        </is>
+      </c>
+      <c r="BU59" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>1</v>
+      </c>
       <c r="BX59" t="inlineStr">
         <is>
           <t>C26n6ttv01-2026-08-05-8909001499832</t>
@@ -21339,6 +21991,25 @@
       <c r="BR60" t="n">
         <v>1</v>
       </c>
+      <c r="BS60" t="inlineStr">
+        <is>
+          <t>C26n6ttv01</t>
+        </is>
+      </c>
+      <c r="BT60" t="inlineStr">
+        <is>
+          <t>8909404064088</t>
+        </is>
+      </c>
+      <c r="BU60" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>1</v>
+      </c>
       <c r="BX60" t="inlineStr">
         <is>
           <t>C26n6ttv01-2026-08-05-8909404064088</t>
@@ -21717,6 +22388,25 @@
       <c r="BR61" t="n">
         <v>1</v>
       </c>
+      <c r="BS61" t="inlineStr">
+        <is>
+          <t>C26n9x8802</t>
+        </is>
+      </c>
+      <c r="BT61" t="inlineStr">
+        <is>
+          <t>8907546805484</t>
+        </is>
+      </c>
+      <c r="BU61" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>1</v>
+      </c>
       <c r="BX61" t="inlineStr">
         <is>
           <t>C26n9x8802-2026-08-05-8907546805484</t>
@@ -22095,6 +22785,25 @@
       <c r="BR62" t="n">
         <v>1</v>
       </c>
+      <c r="BS62" t="inlineStr">
+        <is>
+          <t>C26n9x8802</t>
+        </is>
+      </c>
+      <c r="BT62" t="inlineStr">
+        <is>
+          <t>8907546805484</t>
+        </is>
+      </c>
+      <c r="BU62" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>1</v>
+      </c>
       <c r="BX62" t="inlineStr">
         <is>
           <t>C26n9x8802-2026-08-05-8907546805484</t>
@@ -22473,6 +23182,25 @@
       <c r="BR63" t="n">
         <v>1</v>
       </c>
+      <c r="BS63" t="inlineStr">
+        <is>
+          <t>C26n9x8802</t>
+        </is>
+      </c>
+      <c r="BT63" t="inlineStr">
+        <is>
+          <t>8909001164730</t>
+        </is>
+      </c>
+      <c r="BU63" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>1</v>
+      </c>
       <c r="BX63" t="inlineStr">
         <is>
           <t>C26n9x8802-2026-08-05-8909001164730</t>
@@ -22851,6 +23579,25 @@
       <c r="BR64" t="n">
         <v>1</v>
       </c>
+      <c r="BS64" t="inlineStr">
+        <is>
+          <t>C26n9x8802</t>
+        </is>
+      </c>
+      <c r="BT64" t="inlineStr">
+        <is>
+          <t>8909001164730</t>
+        </is>
+      </c>
+      <c r="BU64" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>1</v>
+      </c>
       <c r="BX64" t="inlineStr">
         <is>
           <t>C26n9x8802-2026-08-05-8909001164730</t>
@@ -23224,6 +23971,25 @@
       <c r="BR65" t="n">
         <v>1</v>
       </c>
+      <c r="BS65" t="inlineStr">
+        <is>
+          <t>C26nd2ok02</t>
+        </is>
+      </c>
+      <c r="BT65" t="inlineStr">
+        <is>
+          <t>8909404240031</t>
+        </is>
+      </c>
+      <c r="BU65" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>1</v>
+      </c>
       <c r="BX65" t="inlineStr">
         <is>
           <t>C26nd2ok02-2026-08-05-8909404240031</t>
@@ -24590,6 +25356,25 @@
       <c r="BR69" t="n">
         <v>1</v>
       </c>
+      <c r="BS69" t="inlineStr">
+        <is>
+          <t>C26o4PQr01</t>
+        </is>
+      </c>
+      <c r="BT69" t="inlineStr">
+        <is>
+          <t>8909001186305</t>
+        </is>
+      </c>
+      <c r="BU69" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>1</v>
+      </c>
       <c r="BX69" t="inlineStr">
         <is>
           <t>C26o4PQr01-2026-08-05-8909001186305</t>
@@ -24968,6 +25753,25 @@
       <c r="BR70" t="n">
         <v>1</v>
       </c>
+      <c r="BS70" t="inlineStr">
+        <is>
+          <t>C26osakk01</t>
+        </is>
+      </c>
+      <c r="BT70" t="inlineStr">
+        <is>
+          <t>8909001921067</t>
+        </is>
+      </c>
+      <c r="BU70" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>1</v>
+      </c>
       <c r="BX70" t="inlineStr">
         <is>
           <t>C26osakk01-2026-08-05-8909001921067</t>
@@ -25341,6 +26145,25 @@
       <c r="BR71" t="n">
         <v>1</v>
       </c>
+      <c r="BS71" t="inlineStr">
+        <is>
+          <t>C26osakk01</t>
+        </is>
+      </c>
+      <c r="BT71" t="inlineStr">
+        <is>
+          <t>8909404248136</t>
+        </is>
+      </c>
+      <c r="BU71" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>1</v>
+      </c>
       <c r="BX71" t="inlineStr">
         <is>
           <t>C26osakk01-2026-08-05-8909404248136</t>
@@ -25714,6 +26537,25 @@
       <c r="BR72" t="n">
         <v>1</v>
       </c>
+      <c r="BS72" t="inlineStr">
+        <is>
+          <t>C26Pddtk01</t>
+        </is>
+      </c>
+      <c r="BT72" t="inlineStr">
+        <is>
+          <t>8909001868782</t>
+        </is>
+      </c>
+      <c r="BU72" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>1</v>
+      </c>
       <c r="BX72" t="inlineStr">
         <is>
           <t>C26Pddtk01-2026-08-05-8909001868782</t>
@@ -26087,6 +26929,25 @@
       <c r="BR73" t="n">
         <v>1</v>
       </c>
+      <c r="BS73" t="inlineStr">
+        <is>
+          <t>C26Pt9Yx01</t>
+        </is>
+      </c>
+      <c r="BT73" t="inlineStr">
+        <is>
+          <t>8909404063265</t>
+        </is>
+      </c>
+      <c r="BU73" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>1</v>
+      </c>
       <c r="BX73" t="inlineStr">
         <is>
           <t>C26Pt9Yx01-2026-08-05-8909404063265</t>
@@ -26460,6 +27321,25 @@
       <c r="BR74" t="n">
         <v>1</v>
       </c>
+      <c r="BS74" t="inlineStr">
+        <is>
+          <t>C26Pt9Yx01</t>
+        </is>
+      </c>
+      <c r="BT74" t="inlineStr">
+        <is>
+          <t>8909404063265</t>
+        </is>
+      </c>
+      <c r="BU74" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>1</v>
+      </c>
       <c r="BX74" t="inlineStr">
         <is>
           <t>C26Pt9Yx01-2026-08-05-8909404063265</t>
@@ -27169,6 +28049,25 @@
       <c r="BR76" t="n">
         <v>1</v>
       </c>
+      <c r="BS76" t="inlineStr">
+        <is>
+          <t>C26Pz4xz01</t>
+        </is>
+      </c>
+      <c r="BT76" t="inlineStr">
+        <is>
+          <t>8909001293683</t>
+        </is>
+      </c>
+      <c r="BU76" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>1</v>
+      </c>
       <c r="BX76" t="inlineStr">
         <is>
           <t>C26Pz4xz01-2026-08-05-8909001293683</t>
@@ -27542,6 +28441,25 @@
       <c r="BR77" t="n">
         <v>1</v>
       </c>
+      <c r="BS77" t="inlineStr">
+        <is>
+          <t>C26Q0wiP02</t>
+        </is>
+      </c>
+      <c r="BT77" t="inlineStr">
+        <is>
+          <t>8909001058961</t>
+        </is>
+      </c>
+      <c r="BU77" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>1</v>
+      </c>
       <c r="BX77" t="inlineStr">
         <is>
           <t>C26Q0wiP02-2026-08-05-8909001058961</t>
@@ -28246,6 +29164,25 @@
       <c r="BR79" t="n">
         <v>1</v>
       </c>
+      <c r="BS79" t="inlineStr">
+        <is>
+          <t>C26QYccc01</t>
+        </is>
+      </c>
+      <c r="BT79" t="inlineStr">
+        <is>
+          <t>8909404210041</t>
+        </is>
+      </c>
+      <c r="BU79" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>1</v>
+      </c>
       <c r="BX79" t="inlineStr">
         <is>
           <t>C26QYccc01-2026-08-05-8909404210041</t>
@@ -28619,6 +29556,25 @@
       <c r="BR80" t="n">
         <v>1</v>
       </c>
+      <c r="BS80" t="inlineStr">
+        <is>
+          <t>C26s1rk001</t>
+        </is>
+      </c>
+      <c r="BT80" t="inlineStr">
+        <is>
+          <t>8909404128377</t>
+        </is>
+      </c>
+      <c r="BU80" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>1</v>
+      </c>
       <c r="BX80" t="inlineStr">
         <is>
           <t>C26s1rk001-2026-08-05-8909404128377</t>
@@ -29328,6 +30284,25 @@
       <c r="BR82" t="n">
         <v>1</v>
       </c>
+      <c r="BS82" t="inlineStr">
+        <is>
+          <t>C26swr6901</t>
+        </is>
+      </c>
+      <c r="BT82" t="inlineStr">
+        <is>
+          <t>8907546903289</t>
+        </is>
+      </c>
+      <c r="BU82" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>1</v>
+      </c>
       <c r="BX82" t="inlineStr">
         <is>
           <t>C26swr6901-2026-08-05-8907546903289</t>
@@ -30032,6 +31007,25 @@
       <c r="BR84" t="n">
         <v>1</v>
       </c>
+      <c r="BS84" t="inlineStr">
+        <is>
+          <t>C26u5ss201</t>
+        </is>
+      </c>
+      <c r="BT84" t="inlineStr">
+        <is>
+          <t>8909001321874</t>
+        </is>
+      </c>
+      <c r="BU84" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>1</v>
+      </c>
       <c r="BX84" t="inlineStr">
         <is>
           <t>C26u5ss201-2026-08-05-8909001321874</t>
@@ -30405,6 +31399,25 @@
       <c r="BR85" t="n">
         <v>1</v>
       </c>
+      <c r="BS85" t="inlineStr">
+        <is>
+          <t>C26uiatd02</t>
+        </is>
+      </c>
+      <c r="BT85" t="inlineStr">
+        <is>
+          <t>8909404196154</t>
+        </is>
+      </c>
+      <c r="BU85" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>1</v>
+      </c>
       <c r="BX85" t="inlineStr">
         <is>
           <t>C26uiatd02-2026-08-05-8909404196154</t>
@@ -31109,6 +32122,25 @@
       <c r="BR87" t="n">
         <v>1</v>
       </c>
+      <c r="BS87" t="inlineStr">
+        <is>
+          <t>C26wl3zf01</t>
+        </is>
+      </c>
+      <c r="BT87" t="inlineStr">
+        <is>
+          <t>8909404251853</t>
+        </is>
+      </c>
+      <c r="BU87" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>1</v>
+      </c>
       <c r="BX87" t="inlineStr">
         <is>
           <t>C26wl3zf01-2026-08-05-8909404251853</t>
@@ -31813,6 +32845,25 @@
       <c r="BR89" t="n">
         <v>1</v>
       </c>
+      <c r="BS89" t="inlineStr">
+        <is>
+          <t>C26xdPJo02</t>
+        </is>
+      </c>
+      <c r="BT89" t="inlineStr">
+        <is>
+          <t>8909404224239</t>
+        </is>
+      </c>
+      <c r="BU89" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>1</v>
+      </c>
       <c r="BX89" t="inlineStr">
         <is>
           <t>C26xdPJo02-2026-08-05-8909404224239</t>
@@ -32191,6 +33242,25 @@
       <c r="BR90" t="n">
         <v>1</v>
       </c>
+      <c r="BS90" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT90" t="inlineStr">
+        <is>
+          <t>8907546992924</t>
+        </is>
+      </c>
+      <c r="BU90" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>1</v>
+      </c>
       <c r="BX90" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8907546992924</t>
@@ -32569,6 +33639,25 @@
       <c r="BR91" t="n">
         <v>1</v>
       </c>
+      <c r="BS91" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT91" t="inlineStr">
+        <is>
+          <t>8907546993136</t>
+        </is>
+      </c>
+      <c r="BU91" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>1</v>
+      </c>
       <c r="BX91" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8907546993136</t>
@@ -32947,6 +34036,25 @@
       <c r="BR92" t="n">
         <v>1</v>
       </c>
+      <c r="BS92" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT92" t="inlineStr">
+        <is>
+          <t>8907546993136</t>
+        </is>
+      </c>
+      <c r="BU92" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>1</v>
+      </c>
       <c r="BX92" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8907546993136</t>
@@ -33325,6 +34433,25 @@
       <c r="BR93" t="n">
         <v>1</v>
       </c>
+      <c r="BS93" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT93" t="inlineStr">
+        <is>
+          <t>8907546993204</t>
+        </is>
+      </c>
+      <c r="BU93" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>1</v>
+      </c>
       <c r="BX93" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8907546993204</t>
@@ -33703,6 +34830,25 @@
       <c r="BR94" t="n">
         <v>1</v>
       </c>
+      <c r="BS94" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT94" t="inlineStr">
+        <is>
+          <t>8907546993204</t>
+        </is>
+      </c>
+      <c r="BU94" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>1</v>
+      </c>
       <c r="BX94" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8907546993204</t>
@@ -34081,6 +35227,25 @@
       <c r="BR95" t="n">
         <v>1</v>
       </c>
+      <c r="BS95" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT95" t="inlineStr">
+        <is>
+          <t>8909001164488</t>
+        </is>
+      </c>
+      <c r="BU95" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>1</v>
+      </c>
       <c r="BX95" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001164488</t>
@@ -34459,6 +35624,25 @@
       <c r="BR96" t="n">
         <v>1</v>
       </c>
+      <c r="BS96" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT96" t="inlineStr">
+        <is>
+          <t>8909001164488</t>
+        </is>
+      </c>
+      <c r="BU96" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>1</v>
+      </c>
       <c r="BX96" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001164488</t>
@@ -34837,6 +36021,25 @@
       <c r="BR97" t="n">
         <v>1</v>
       </c>
+      <c r="BS97" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT97" t="inlineStr">
+        <is>
+          <t>8909001164761</t>
+        </is>
+      </c>
+      <c r="BU97" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>1</v>
+      </c>
       <c r="BX97" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001164761</t>
@@ -35215,6 +36418,25 @@
       <c r="BR98" t="n">
         <v>1</v>
       </c>
+      <c r="BS98" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT98" t="inlineStr">
+        <is>
+          <t>8909001164761</t>
+        </is>
+      </c>
+      <c r="BU98" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>1</v>
+      </c>
       <c r="BX98" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001164761</t>
@@ -35593,6 +36815,25 @@
       <c r="BR99" t="n">
         <v>1</v>
       </c>
+      <c r="BS99" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT99" t="inlineStr">
+        <is>
+          <t>8909001287217</t>
+        </is>
+      </c>
+      <c r="BU99" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>1</v>
+      </c>
       <c r="BX99" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001287217</t>
@@ -35971,6 +37212,25 @@
       <c r="BR100" t="n">
         <v>1</v>
       </c>
+      <c r="BS100" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT100" t="inlineStr">
+        <is>
+          <t>8909001287217</t>
+        </is>
+      </c>
+      <c r="BU100" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>1</v>
+      </c>
       <c r="BX100" t="inlineStr">
         <is>
           <t>C26Y95ro02-2026-08-05-8909001287217</t>
@@ -36347,6 +37607,25 @@
         <v>46239</v>
       </c>
       <c r="BR101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS101" t="inlineStr">
+        <is>
+          <t>C26Y95ro02</t>
+        </is>
+      </c>
+      <c r="BT101" t="inlineStr">
+        <is>
+          <t>8909001724538</t>
+        </is>
+      </c>
+      <c r="BU101" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>3289</v>
+      </c>
+      <c r="BW101" t="n">
         <v>1</v>
       </c>
       <c r="BX101" t="inlineStr">
